--- a/Team-Data/2011-12/4-3-2011-12.xlsx
+++ b/Team-Data/2011-12/4-3-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,16 +806,16 @@
         <v>1.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF2" t="n">
         <v>11</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH2" t="n">
         <v>1</v>
@@ -769,7 +836,7 @@
         <v>13</v>
       </c>
       <c r="AN2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO2" t="n">
         <v>28</v>
@@ -781,10 +848,10 @@
         <v>24</v>
       </c>
       <c r="AR2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT2" t="n">
         <v>23</v>
@@ -802,7 +869,7 @@
         <v>21</v>
       </c>
       <c r="AY2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ2" t="n">
         <v>6</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -921,22 +988,22 @@
         <v>1.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
         <v>10</v>
       </c>
       <c r="AF3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG3" t="n">
         <v>9</v>
       </c>
       <c r="AH3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -948,7 +1015,7 @@
         <v>24</v>
       </c>
       <c r="AM3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN3" t="n">
         <v>9</v>
@@ -978,10 +1045,10 @@
         <v>17</v>
       </c>
       <c r="AW3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -1025,28 +1092,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E4" t="n">
         <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
-        <v>0.137</v>
+        <v>0.14</v>
       </c>
       <c r="H4" t="n">
         <v>48.2</v>
       </c>
       <c r="I4" t="n">
-        <v>33.5</v>
+        <v>33.6</v>
       </c>
       <c r="J4" t="n">
         <v>80.8</v>
       </c>
       <c r="K4" t="n">
-        <v>0.415</v>
+        <v>0.416</v>
       </c>
       <c r="L4" t="n">
         <v>4.1</v>
@@ -1055,25 +1122,25 @@
         <v>13.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0.301</v>
+        <v>0.3</v>
       </c>
       <c r="O4" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P4" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.752</v>
+        <v>0.753</v>
       </c>
       <c r="R4" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="S4" t="n">
         <v>28.9</v>
       </c>
       <c r="T4" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="U4" t="n">
         <v>20.6</v>
@@ -1085,10 +1152,10 @@
         <v>6.4</v>
       </c>
       <c r="X4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z4" t="n">
         <v>19.5</v>
@@ -1100,7 +1167,7 @@
         <v>87.90000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-12.5</v>
+        <v>-12.7</v>
       </c>
       <c r="AD4" t="n">
         <v>28</v>
@@ -1121,7 +1188,7 @@
         <v>30</v>
       </c>
       <c r="AJ4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK4" t="n">
         <v>30</v>
@@ -1136,16 +1203,16 @@
         <v>30</v>
       </c>
       <c r="AO4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP4" t="n">
         <v>15</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>14</v>
       </c>
       <c r="AQ4" t="n">
         <v>18</v>
       </c>
       <c r="AR4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AS4" t="n">
         <v>28</v>
@@ -1163,10 +1230,10 @@
         <v>29</v>
       </c>
       <c r="AX4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AZ4" t="n">
         <v>12</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="AH5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI5" t="n">
         <v>9</v>
@@ -1309,7 +1376,7 @@
         <v>9</v>
       </c>
       <c r="AL5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM5" t="n">
         <v>19</v>
@@ -1318,7 +1385,7 @@
         <v>4</v>
       </c>
       <c r="AO5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP5" t="n">
         <v>21</v>
@@ -1357,7 +1424,7 @@
         <v>28</v>
       </c>
       <c r="BB5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC5" t="n">
         <v>1</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E6" t="n">
         <v>17</v>
       </c>
       <c r="F6" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G6" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="H6" t="n">
         <v>48.3</v>
@@ -1413,34 +1480,34 @@
         <v>0.423</v>
       </c>
       <c r="L6" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M6" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N6" t="n">
         <v>0.349</v>
       </c>
       <c r="O6" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="P6" t="n">
-        <v>25.3</v>
+        <v>25.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.705</v>
+        <v>0.703</v>
       </c>
       <c r="R6" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="S6" t="n">
-        <v>29.8</v>
+        <v>30</v>
       </c>
       <c r="T6" t="n">
-        <v>42.6</v>
+        <v>42.9</v>
       </c>
       <c r="U6" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V6" t="n">
         <v>15.4</v>
@@ -1449,22 +1516,22 @@
         <v>7.4</v>
       </c>
       <c r="X6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y6" t="n">
         <v>6.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.2</v>
+        <v>93.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>-6.5</v>
+        <v>-5.9</v>
       </c>
       <c r="AD6" t="n">
         <v>28</v>
@@ -1473,10 +1540,10 @@
         <v>27</v>
       </c>
       <c r="AF6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH6" t="n">
         <v>18</v>
@@ -1494,7 +1561,7 @@
         <v>14</v>
       </c>
       <c r="AM6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN6" t="n">
         <v>13</v>
@@ -1512,31 +1579,31 @@
         <v>4</v>
       </c>
       <c r="AS6" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AT6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU6" t="n">
         <v>21</v>
       </c>
       <c r="AV6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW6" t="n">
         <v>18</v>
       </c>
       <c r="AX6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AY6" t="n">
         <v>29</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>28</v>
       </c>
       <c r="AZ6" t="n">
         <v>23</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB6" t="n">
         <v>23</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -1649,19 +1716,19 @@
         <v>1</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>10</v>
       </c>
       <c r="AF7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI7" t="n">
         <v>20</v>
@@ -1697,7 +1764,7 @@
         <v>5</v>
       </c>
       <c r="AT7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU7" t="n">
         <v>13</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -1831,16 +1898,16 @@
         <v>1.5</v>
       </c>
       <c r="AD8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG8" t="n">
         <v>14</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>13</v>
       </c>
       <c r="AH8" t="n">
         <v>3</v>
@@ -1858,7 +1925,7 @@
         <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN8" t="n">
         <v>23</v>
@@ -1873,7 +1940,7 @@
         <v>22</v>
       </c>
       <c r="AR8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS8" t="n">
         <v>4</v>
@@ -1897,7 +1964,7 @@
         <v>30</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
         <v>2</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -1935,28 +2002,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F9" t="n">
         <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>0.377</v>
+        <v>0.365</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>34.6</v>
+        <v>34.4</v>
       </c>
       <c r="J9" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="K9" t="n">
-        <v>0.436</v>
+        <v>0.434</v>
       </c>
       <c r="L9" t="n">
         <v>4.5</v>
@@ -1965,28 +2032,28 @@
         <v>13</v>
       </c>
       <c r="N9" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O9" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P9" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="R9" t="n">
         <v>11.9</v>
       </c>
       <c r="S9" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="U9" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="V9" t="n">
         <v>15.7</v>
@@ -1998,25 +2065,25 @@
         <v>4.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z9" t="n">
         <v>19.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>90.09999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>-5.3</v>
+        <v>-5.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AE9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF9" t="n">
         <v>23</v>
@@ -2034,7 +2101,7 @@
         <v>24</v>
       </c>
       <c r="AK9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL9" t="n">
         <v>26</v>
@@ -2046,13 +2113,13 @@
         <v>17</v>
       </c>
       <c r="AO9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP9" t="n">
         <v>17</v>
       </c>
       <c r="AQ9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AR9" t="n">
         <v>11</v>
@@ -2079,7 +2146,7 @@
         <v>21</v>
       </c>
       <c r="AZ9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA9" t="n">
         <v>17</v>
@@ -2088,7 +2155,7 @@
         <v>28</v>
       </c>
       <c r="BC9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" t="n">
         <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G10" t="n">
-        <v>0.385</v>
+        <v>0.392</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
@@ -2135,7 +2202,7 @@
         <v>37.3</v>
       </c>
       <c r="J10" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K10" t="n">
         <v>0.457</v>
@@ -2156,19 +2223,19 @@
         <v>19.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.775</v>
+        <v>0.776</v>
       </c>
       <c r="R10" t="n">
         <v>9.6</v>
       </c>
       <c r="S10" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T10" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="U10" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="V10" t="n">
         <v>13.8</v>
@@ -2180,10 +2247,10 @@
         <v>5.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AA10" t="n">
         <v>17.1</v>
@@ -2195,7 +2262,7 @@
         <v>-2.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE10" t="n">
         <v>22</v>
@@ -2210,7 +2277,7 @@
         <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ10" t="n">
         <v>11</v>
@@ -2255,10 +2322,10 @@
         <v>12</v>
       </c>
       <c r="AX10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY10" t="n">
         <v>8</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>11</v>
       </c>
       <c r="AZ10" t="n">
         <v>27</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -2377,10 +2444,10 @@
         <v>0.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF11" t="n">
         <v>15</v>
@@ -2392,7 +2459,7 @@
         <v>4</v>
       </c>
       <c r="AI11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ11" t="n">
         <v>5</v>
@@ -2404,7 +2471,7 @@
         <v>12</v>
       </c>
       <c r="AM11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -2481,43 +2548,43 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F12" t="n">
         <v>21</v>
       </c>
       <c r="G12" t="n">
-        <v>0.604</v>
+        <v>0.596</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="J12" t="n">
-        <v>80.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="K12" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L12" t="n">
         <v>5.8</v>
       </c>
       <c r="M12" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.367</v>
+        <v>0.37</v>
       </c>
       <c r="O12" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="P12" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="Q12" t="n">
         <v>0.777</v>
@@ -2535,7 +2602,7 @@
         <v>18.3</v>
       </c>
       <c r="V12" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W12" t="n">
         <v>7.9</v>
@@ -2550,31 +2617,31 @@
         <v>21.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>96.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AE12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF12" t="n">
         <v>6</v>
       </c>
       <c r="AG12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AH12" t="n">
         <v>11</v>
       </c>
       <c r="AI12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ12" t="n">
         <v>21</v>
@@ -2589,7 +2656,7 @@
         <v>22</v>
       </c>
       <c r="AN12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO12" t="n">
         <v>3</v>
@@ -2604,10 +2671,10 @@
         <v>8</v>
       </c>
       <c r="AS12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU12" t="n">
         <v>30</v>
@@ -2619,7 +2686,7 @@
         <v>14</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY12" t="n">
         <v>27</v>
@@ -2628,13 +2695,13 @@
         <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB12" t="n">
         <v>16</v>
       </c>
       <c r="BC12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>2.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AE13" t="n">
         <v>6</v>
@@ -2777,7 +2844,7 @@
         <v>18</v>
       </c>
       <c r="AP13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ13" t="n">
         <v>29</v>
@@ -2789,7 +2856,7 @@
         <v>24</v>
       </c>
       <c r="AT13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU13" t="n">
         <v>15</v>
@@ -2807,13 +2874,13 @@
         <v>6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA13" t="n">
         <v>4</v>
       </c>
       <c r="BB13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC13" t="n">
         <v>9</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -2845,22 +2912,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E14" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F14" t="n">
         <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>0.63</v>
+        <v>0.623</v>
       </c>
       <c r="H14" t="n">
         <v>48.6</v>
       </c>
       <c r="I14" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J14" t="n">
         <v>79.5</v>
@@ -2872,40 +2939,40 @@
         <v>5.5</v>
       </c>
       <c r="M14" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="N14" t="n">
         <v>0.317</v>
       </c>
       <c r="O14" t="n">
-        <v>18.1</v>
+        <v>18.4</v>
       </c>
       <c r="P14" t="n">
-        <v>23.9</v>
+        <v>24.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="R14" t="n">
         <v>11.7</v>
       </c>
       <c r="S14" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="T14" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
       <c r="U14" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="V14" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="X14" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y14" t="n">
         <v>4.2</v>
@@ -2914,16 +2981,16 @@
         <v>17.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>96.2</v>
+        <v>96.3</v>
       </c>
       <c r="AC14" t="n">
         <v>2.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2953,7 +3020,7 @@
         <v>18</v>
       </c>
       <c r="AN14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO14" t="n">
         <v>8</v>
@@ -2962,10 +3029,10 @@
         <v>9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS14" t="n">
         <v>1</v>
@@ -2977,13 +3044,13 @@
         <v>8</v>
       </c>
       <c r="AV14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AW14" t="n">
         <v>30</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AY14" t="n">
         <v>3</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15" t="n">
         <v>22</v>
       </c>
       <c r="G15" t="n">
-        <v>0.577</v>
+        <v>0.569</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
@@ -3045,19 +3112,19 @@
         <v>36.9</v>
       </c>
       <c r="J15" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="K15" t="n">
         <v>0.446</v>
       </c>
       <c r="L15" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="M15" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="N15" t="n">
-        <v>0.32</v>
+        <v>0.314</v>
       </c>
       <c r="O15" t="n">
         <v>17.5</v>
@@ -3066,7 +3133,7 @@
         <v>23.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.753</v>
+        <v>0.756</v>
       </c>
       <c r="R15" t="n">
         <v>12.5</v>
@@ -3087,16 +3154,16 @@
         <v>9.9</v>
       </c>
       <c r="X15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y15" t="n">
         <v>5.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB15" t="n">
         <v>95.2</v>
@@ -3105,16 +3172,16 @@
         <v>1.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AH15" t="n">
         <v>10</v>
@@ -3129,13 +3196,13 @@
         <v>15</v>
       </c>
       <c r="AL15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM15" t="n">
         <v>29</v>
       </c>
       <c r="AN15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO15" t="n">
         <v>11</v>
@@ -3153,7 +3220,7 @@
         <v>22</v>
       </c>
       <c r="AT15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU15" t="n">
         <v>24</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F16" t="n">
         <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>0.731</v>
+        <v>0.725</v>
       </c>
       <c r="H16" t="n">
         <v>48.7</v>
@@ -3227,28 +3294,28 @@
         <v>37.8</v>
       </c>
       <c r="J16" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.478</v>
+        <v>0.479</v>
       </c>
       <c r="L16" t="n">
         <v>5.6</v>
       </c>
       <c r="M16" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0.371</v>
+        <v>0.374</v>
       </c>
       <c r="O16" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="P16" t="n">
-        <v>25.2</v>
+        <v>25</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.775</v>
+        <v>0.774</v>
       </c>
       <c r="R16" t="n">
         <v>10.2</v>
@@ -3260,13 +3327,13 @@
         <v>41.8</v>
       </c>
       <c r="U16" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V16" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W16" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="X16" t="n">
         <v>5.4</v>
@@ -3275,7 +3342,7 @@
         <v>4.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA16" t="n">
         <v>20.8</v>
@@ -3287,7 +3354,7 @@
         <v>7.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3302,7 +3369,7 @@
         <v>5</v>
       </c>
       <c r="AI16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ16" t="n">
         <v>25</v>
@@ -3326,19 +3393,19 @@
         <v>7</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS16" t="n">
         <v>10</v>
       </c>
       <c r="AT16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV16" t="n">
         <v>18</v>
@@ -3350,7 +3417,7 @@
         <v>9</v>
       </c>
       <c r="AY16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ16" t="n">
         <v>17</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>0.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
@@ -3529,10 +3596,10 @@
         <v>8</v>
       </c>
       <c r="AX17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ17" t="n">
         <v>13</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3739,7 @@
         <v>10</v>
       </c>
       <c r="AK18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL18" t="n">
         <v>8</v>
@@ -3681,7 +3748,7 @@
         <v>6</v>
       </c>
       <c r="AN18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO18" t="n">
         <v>4</v>
@@ -3690,7 +3757,7 @@
         <v>5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR18" t="n">
         <v>7</v>
@@ -3705,13 +3772,13 @@
         <v>25</v>
       </c>
       <c r="AV18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW18" t="n">
         <v>25</v>
       </c>
       <c r="AX18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY18" t="n">
         <v>22</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E19" t="n">
         <v>19</v>
       </c>
       <c r="F19" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G19" t="n">
-        <v>0.345</v>
+        <v>0.352</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
@@ -3773,7 +3840,7 @@
         <v>34</v>
       </c>
       <c r="J19" t="n">
-        <v>80</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K19" t="n">
         <v>0.425</v>
@@ -3782,34 +3849,34 @@
         <v>8.1</v>
       </c>
       <c r="M19" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="N19" t="n">
         <v>0.345</v>
       </c>
       <c r="O19" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P19" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R19" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S19" t="n">
         <v>28.2</v>
       </c>
       <c r="T19" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="U19" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V19" t="n">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="W19" t="n">
         <v>7.6</v>
@@ -3818,31 +3885,31 @@
         <v>4.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>93</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC19" t="n">
         <v>-5.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH19" t="n">
         <v>28</v>
@@ -3869,7 +3936,7 @@
         <v>13</v>
       </c>
       <c r="AP19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ19" t="n">
         <v>11</v>
@@ -3887,19 +3954,19 @@
         <v>22</v>
       </c>
       <c r="AV19" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AW19" t="n">
         <v>16</v>
       </c>
       <c r="AX19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA19" t="n">
         <v>16</v>
@@ -3908,7 +3975,7 @@
         <v>25</v>
       </c>
       <c r="BC19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-4.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
@@ -4039,7 +4106,7 @@
         <v>14</v>
       </c>
       <c r="AL20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM20" t="n">
         <v>30</v>
@@ -4060,25 +4127,25 @@
         <v>16</v>
       </c>
       <c r="AS20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT20" t="n">
         <v>24</v>
       </c>
       <c r="AU20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX20" t="n">
         <v>22</v>
       </c>
       <c r="AY20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ20" t="n">
         <v>19</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -4119,37 +4186,37 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E21" t="n">
         <v>27</v>
       </c>
       <c r="F21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5</v>
+        <v>0.509</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="J21" t="n">
         <v>80.8</v>
       </c>
       <c r="K21" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L21" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M21" t="n">
         <v>22.6</v>
       </c>
       <c r="N21" t="n">
-        <v>0.317</v>
+        <v>0.315</v>
       </c>
       <c r="O21" t="n">
         <v>19.3</v>
@@ -4158,19 +4225,19 @@
         <v>25.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.744</v>
+        <v>0.745</v>
       </c>
       <c r="R21" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S21" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T21" t="n">
         <v>42.6</v>
       </c>
       <c r="U21" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="V21" t="n">
         <v>16.6</v>
@@ -4179,43 +4246,43 @@
         <v>9.6</v>
       </c>
       <c r="X21" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y21" t="n">
         <v>4.9</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AA21" t="n">
         <v>22.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>97.2</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE21" t="n">
         <v>17</v>
       </c>
       <c r="AF21" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
       </c>
       <c r="AJ21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK21" t="n">
         <v>23</v>
@@ -4227,7 +4294,7 @@
         <v>3</v>
       </c>
       <c r="AN21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO21" t="n">
         <v>6</v>
@@ -4239,13 +4306,13 @@
         <v>21</v>
       </c>
       <c r="AR21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT21" t="n">
         <v>12</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>10</v>
       </c>
       <c r="AU21" t="n">
         <v>23</v>
@@ -4263,16 +4330,16 @@
         <v>15</v>
       </c>
       <c r="AZ21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA21" t="n">
         <v>1</v>
       </c>
       <c r="BB21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BC21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>6.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,7 +4458,7 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI22" t="n">
         <v>7</v>
@@ -4403,7 +4470,7 @@
         <v>2</v>
       </c>
       <c r="AL22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM22" t="n">
         <v>12</v>
@@ -4421,13 +4488,13 @@
         <v>1</v>
       </c>
       <c r="AR22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS22" t="n">
         <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU22" t="n">
         <v>28</v>
@@ -4442,7 +4509,7 @@
         <v>1</v>
       </c>
       <c r="AY22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ22" t="n">
         <v>20</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -4483,61 +4550,61 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E23" t="n">
         <v>32</v>
       </c>
       <c r="F23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G23" t="n">
-        <v>0.593</v>
+        <v>0.604</v>
       </c>
       <c r="H23" t="n">
         <v>48.4</v>
       </c>
       <c r="I23" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="J23" t="n">
-        <v>77.40000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="K23" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L23" t="n">
         <v>10.2</v>
       </c>
       <c r="M23" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="N23" t="n">
         <v>0.38</v>
       </c>
       <c r="O23" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="P23" t="n">
         <v>23.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.648</v>
+        <v>0.645</v>
       </c>
       <c r="R23" t="n">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
       <c r="S23" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>42.6</v>
+        <v>42.8</v>
       </c>
       <c r="U23" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V23" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W23" t="n">
         <v>6.7</v>
@@ -4558,22 +4625,22 @@
         <v>94.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE23" t="n">
         <v>6</v>
       </c>
       <c r="AF23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AH23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI23" t="n">
         <v>27</v>
@@ -4594,31 +4661,31 @@
         <v>3</v>
       </c>
       <c r="AO23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AS23" t="n">
         <v>9</v>
       </c>
       <c r="AT23" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AU23" t="n">
         <v>20</v>
       </c>
       <c r="AV23" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AW23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX23" t="n">
         <v>26</v>
@@ -4627,10 +4694,10 @@
         <v>1</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB23" t="n">
         <v>21</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E24" t="n">
         <v>29</v>
       </c>
       <c r="F24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G24" t="n">
-        <v>0.547</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
@@ -4689,13 +4756,13 @@
         <v>0.448</v>
       </c>
       <c r="L24" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="M24" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="O24" t="n">
         <v>13</v>
@@ -4704,22 +4771,22 @@
         <v>17.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.736</v>
+        <v>0.734</v>
       </c>
       <c r="R24" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S24" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T24" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="U24" t="n">
         <v>21.8</v>
       </c>
       <c r="V24" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="W24" t="n">
         <v>8.300000000000001</v>
@@ -4731,34 +4798,34 @@
         <v>4.9</v>
       </c>
       <c r="Z24" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="AB24" t="n">
         <v>93.59999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AE24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG24" t="n">
         <v>12</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>13</v>
       </c>
       <c r="AH24" t="n">
         <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ24" t="n">
         <v>4</v>
@@ -4767,13 +4834,13 @@
         <v>13</v>
       </c>
       <c r="AL24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM24" t="n">
         <v>25</v>
       </c>
       <c r="AN24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4791,7 +4858,7 @@
         <v>2</v>
       </c>
       <c r="AT24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AU24" t="n">
         <v>9</v>
@@ -4800,16 +4867,16 @@
         <v>1</v>
       </c>
       <c r="AW24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX24" t="n">
         <v>18</v>
       </c>
       <c r="AY24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -4847,28 +4914,28 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F25" t="n">
         <v>26</v>
       </c>
       <c r="G25" t="n">
-        <v>0.509</v>
+        <v>0.5</v>
       </c>
       <c r="H25" t="n">
         <v>48</v>
       </c>
       <c r="I25" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J25" t="n">
-        <v>81.7</v>
+        <v>81.5</v>
       </c>
       <c r="K25" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L25" t="n">
         <v>6.5</v>
@@ -4877,16 +4944,16 @@
         <v>19.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.337</v>
+        <v>0.34</v>
       </c>
       <c r="O25" t="n">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="P25" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.758</v>
+        <v>0.756</v>
       </c>
       <c r="R25" t="n">
         <v>10.7</v>
@@ -4895,7 +4962,7 @@
         <v>30.9</v>
       </c>
       <c r="T25" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="U25" t="n">
         <v>22.6</v>
@@ -4904,37 +4971,37 @@
         <v>14.2</v>
       </c>
       <c r="W25" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X25" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y25" t="n">
         <v>4.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AA25" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>96.90000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AE25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF25" t="n">
         <v>16</v>
       </c>
       <c r="AG25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH25" t="n">
         <v>30</v>
@@ -4955,7 +5022,7 @@
         <v>17</v>
       </c>
       <c r="AN25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO25" t="n">
         <v>19</v>
@@ -4964,16 +5031,16 @@
         <v>22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AR25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU25" t="n">
         <v>6</v>
@@ -4982,13 +5049,13 @@
         <v>11</v>
       </c>
       <c r="AW25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ25" t="n">
         <v>7</v>
@@ -4997,7 +5064,7 @@
         <v>19</v>
       </c>
       <c r="BB25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC25" t="n">
         <v>20</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>0.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
         <v>19</v>
@@ -5119,7 +5186,7 @@
         <v>20</v>
       </c>
       <c r="AH26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI26" t="n">
         <v>15</v>
@@ -5149,7 +5216,7 @@
         <v>2</v>
       </c>
       <c r="AR26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS26" t="n">
         <v>25</v>
@@ -5170,7 +5237,7 @@
         <v>15</v>
       </c>
       <c r="AY26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ26" t="n">
         <v>16</v>
@@ -5179,7 +5246,7 @@
         <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC26" t="n">
         <v>16</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -5211,46 +5278,46 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E27" t="n">
         <v>19</v>
       </c>
       <c r="F27" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G27" t="n">
-        <v>0.352</v>
+        <v>0.358</v>
       </c>
       <c r="H27" t="n">
         <v>48.3</v>
       </c>
       <c r="I27" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J27" t="n">
         <v>86.5</v>
       </c>
       <c r="K27" t="n">
-        <v>0.432</v>
+        <v>0.431</v>
       </c>
       <c r="L27" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M27" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0.311</v>
+        <v>0.313</v>
       </c>
       <c r="O27" t="n">
         <v>17.8</v>
       </c>
       <c r="P27" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.748</v>
+        <v>0.75</v>
       </c>
       <c r="R27" t="n">
         <v>13.7</v>
@@ -5262,7 +5329,7 @@
         <v>43.5</v>
       </c>
       <c r="U27" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="V27" t="n">
         <v>14.7</v>
@@ -5271,28 +5338,28 @@
         <v>8.300000000000001</v>
       </c>
       <c r="X27" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y27" t="n">
         <v>6.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AB27" t="n">
         <v>98.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>-5.4</v>
+        <v>-5.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF27" t="n">
         <v>25</v>
@@ -5301,10 +5368,10 @@
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ27" t="n">
         <v>1</v>
@@ -5313,10 +5380,10 @@
         <v>27</v>
       </c>
       <c r="AL27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN27" t="n">
         <v>28</v>
@@ -5325,16 +5392,16 @@
         <v>10</v>
       </c>
       <c r="AP27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR27" t="n">
         <v>2</v>
       </c>
       <c r="AS27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT27" t="n">
         <v>6</v>
@@ -5343,19 +5410,19 @@
         <v>26</v>
       </c>
       <c r="AV27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA27" t="n">
         <v>9</v>
@@ -5364,7 +5431,7 @@
         <v>7</v>
       </c>
       <c r="BC27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -5393,82 +5460,82 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E28" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F28" t="n">
         <v>14</v>
       </c>
       <c r="G28" t="n">
-        <v>0.725</v>
+        <v>0.72</v>
       </c>
       <c r="H28" t="n">
         <v>48.4</v>
       </c>
       <c r="I28" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="J28" t="n">
-        <v>82.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="K28" t="n">
-        <v>0.471</v>
+        <v>0.468</v>
       </c>
       <c r="L28" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="N28" t="n">
-        <v>0.391</v>
+        <v>0.389</v>
       </c>
       <c r="O28" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="P28" t="n">
         <v>21.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.729</v>
+        <v>0.727</v>
       </c>
       <c r="R28" t="n">
         <v>10.4</v>
       </c>
       <c r="S28" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="T28" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U28" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V28" t="n">
         <v>13.3</v>
       </c>
       <c r="W28" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X28" t="n">
         <v>4.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>101.9</v>
+        <v>101.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="AD28" t="n">
         <v>28</v>
@@ -5504,7 +5571,7 @@
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP28" t="n">
         <v>20</v>
@@ -5519,7 +5586,7 @@
         <v>7</v>
       </c>
       <c r="AT28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AU28" t="n">
         <v>5</v>
@@ -5528,13 +5595,13 @@
         <v>2</v>
       </c>
       <c r="AW28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX28" t="n">
         <v>25</v>
       </c>
       <c r="AY28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F29" t="n">
         <v>35</v>
       </c>
       <c r="G29" t="n">
-        <v>0.352</v>
+        <v>0.34</v>
       </c>
       <c r="H29" t="n">
         <v>48.5</v>
@@ -5602,19 +5669,19 @@
         <v>5.5</v>
       </c>
       <c r="M29" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0.335</v>
+        <v>0.334</v>
       </c>
       <c r="O29" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P29" t="n">
         <v>21.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.772</v>
+        <v>0.774</v>
       </c>
       <c r="R29" t="n">
         <v>10.5</v>
@@ -5623,19 +5690,19 @@
         <v>30.8</v>
       </c>
       <c r="T29" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U29" t="n">
         <v>21.4</v>
       </c>
       <c r="V29" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W29" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X29" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y29" t="n">
         <v>4.8</v>
@@ -5650,22 +5717,22 @@
         <v>91.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.6</v>
+        <v>-3.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE29" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG29" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AH29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI29" t="n">
         <v>25</v>
@@ -5677,7 +5744,7 @@
         <v>19</v>
       </c>
       <c r="AL29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM29" t="n">
         <v>20</v>
@@ -5692,7 +5759,7 @@
         <v>16</v>
       </c>
       <c r="AQ29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR29" t="n">
         <v>23</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-0.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
         <v>16</v>
@@ -5874,7 +5941,7 @@
         <v>8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR30" t="n">
         <v>3</v>
@@ -5898,7 +5965,7 @@
         <v>4</v>
       </c>
       <c r="AY30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ30" t="n">
         <v>29</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-6.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6050,7 +6117,7 @@
         <v>24</v>
       </c>
       <c r="AO31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP31" t="n">
         <v>19</v>
@@ -6059,19 +6126,19 @@
         <v>26</v>
       </c>
       <c r="AR31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT31" t="n">
         <v>20</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>21</v>
       </c>
       <c r="AU31" t="n">
         <v>28</v>
       </c>
       <c r="AV31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW31" t="n">
         <v>15</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-3-2011-12</t>
+          <t>2012-04-03</t>
         </is>
       </c>
     </row>
